--- a/examples/SmallDrugCombo_Zhou_CellChemBio_2026/raw_data/0077_1uM_9545 combo_Treatment.xlsx
+++ b/examples/SmallDrugCombo_Zhou_CellChemBio_2026/raw_data/0077_1uM_9545 combo_Treatment.xlsx
@@ -16,13 +16,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3">
   <si>
-    <t>G02967907.1-49</t>
+    <t>G00101</t>
   </si>
   <si>
     <t>vehicle</t>
   </si>
   <si>
-    <t>G03069545.15-4</t>
+    <t>G00102</t>
   </si>
 </sst>
 </file>
